--- a/TestData/LV_T2021_GiftApprovalProcessApproveGiftsApproveOrDenyMultipleGiftRequests.xlsx
+++ b/TestData/LV_T2021_GiftApprovalProcessApproveGiftsApproveOrDenyMultipleGiftRequests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DDDDCC-D7B6-4D13-B628-ACF28AC092E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC2A20E-5F86-4488-A064-C63E1494FDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="5" r:id="rId1"/>
@@ -559,6 +559,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DF7EAFE-4697-4E95-8E40-0C3764736EDA}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
